--- a/src/attributions/attributions_ig_traj_407.xlsx
+++ b/src/attributions/attributions_ig_traj_407.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG10"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,25 +999,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.2866420395821815</v>
+        <v>-0.3816215822701564</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1945578972518633</v>
+        <v>0.2769597604421297</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0188155169902699</v>
+        <v>0.01169324700215431</v>
       </c>
       <c r="F2" t="n">
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1029,22 +1029,22 @@
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.01739718412468305</v>
+        <v>-0.0332409325059732</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1370390370430217</v>
+        <v>0.2338735816488058</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02222200155177658</v>
+        <v>0.02981311438969395</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>-0</v>
@@ -1053,100 +1053,100 @@
         <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.176150924410681</v>
+        <v>-0.1931716795571571</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.00905547199555682</v>
+        <v>0.06490833812487067</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.05561933711784186</v>
+        <v>0.01530151557645812</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1754812767241206</v>
+        <v>0.1480654112400233</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1227773471961073</v>
+        <v>0.347748539033526</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01142577902149423</v>
+        <v>-0.1468188981498076</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.07688540209790079</v>
+        <v>-0.2940826034650262</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.06222734730848131</v>
+        <v>0.1102846152218362</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.09636371615648319</v>
+        <v>-0.3779782478420289</v>
       </c>
       <c r="AP2" t="n">
         <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.3541572153581515</v>
+        <v>-0.5162416425071319</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1164550779151879</v>
+        <v>0.4770347271360897</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.106256101911847</v>
+        <v>0.1594715697159847</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
@@ -1158,25 +1158,25 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.08613931906015006</v>
+        <v>0.01610071693225071</v>
       </c>
       <c r="BE2" t="n">
         <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1393912396591787</v>
+        <v>0.05236161160147554</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.07912485653417058</v>
+        <v>0.02301149514690466</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
@@ -1185,25 +1185,25 @@
         <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.06112938263179609</v>
+        <v>0.2212303094753787</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.04958811787198927</v>
+        <v>0.06504059869564119</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.2053891352496053</v>
+        <v>0.0235734963991864</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR2" t="n">
         <v>-0</v>
@@ -1218,16 +1218,16 @@
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.1277921232322891</v>
+        <v>-0.3231746047738231</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.04652011501666443</v>
+        <v>0.2163453985643025</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.04505323252689231</v>
+        <v>0.01498654757647139</v>
       </c>
       <c r="BZ2" t="n">
         <v>-0</v>
@@ -1242,25 +1242,25 @@
         <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1382676905597184</v>
+        <v>0.344386612364371</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.06581790993074962</v>
+        <v>-0.2341397186750342</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.02333586549242133</v>
+        <v>0.07370970314066298</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
         <v>-0</v>
@@ -1272,52 +1272,52 @@
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01800263742345067</v>
+        <v>0.1778361114808734</v>
       </c>
       <c r="CO2" t="n">
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.05564574236990986</v>
+        <v>-0.2823913726841479</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.1013581495609994</v>
+        <v>-0.0004425735128111381</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV2" t="n">
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.1578140898955597</v>
+        <v>0.3535087447026233</v>
       </c>
       <c r="CX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.08411589982593685</v>
+        <v>-0.2570251707960797</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01103141297951243</v>
+        <v>0.02846142199238918</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>-0</v>
@@ -1326,16 +1326,16 @@
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.07726956208184538</v>
+        <v>0.1004402736265913</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.09549844448378844</v>
+        <v>-0.184247221863329</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0664135582878146</v>
+        <v>0.005388713407777354</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
@@ -1350,19 +1350,19 @@
         <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.04052846839844308</v>
+        <v>0.1031337357263051</v>
       </c>
       <c r="DP2" t="n">
         <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.05923241428287763</v>
+        <v>-0.1661662262852208</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.09901851965897598</v>
+        <v>-0.07249888721783436</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
@@ -1377,52 +1377,52 @@
         <v>-0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1963708529889682</v>
+        <v>-0.1421789819976749</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.09223841154068566</v>
+        <v>0.1114890282117382</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.00482827039431469</v>
+        <v>0.08193953783945153</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.08782184408990792</v>
+        <v>0.3551610173625209</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.05665384438500057</v>
+        <v>-0.2119267808051367</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.1727924622305627</v>
+        <v>-0.01483870147178039</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>-0</v>
@@ -1431,28 +1431,28 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.0775441355574803</v>
+        <v>0.2444396775752141</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.07799904254615266</v>
+        <v>-0.1028553478556574</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.007686055847937266</v>
+        <v>0.08511585522201939</v>
       </c>
       <c r="ET2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
@@ -1461,22 +1461,22 @@
         <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.1539043569848971</v>
+        <v>0.3874804431881191</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.07228609920746044</v>
+        <v>-0.3007257943205356</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02047261039560837</v>
+        <v>0.06900249863080218</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
         <v>-0</v>
@@ -1488,16 +1488,16 @@
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.02387424880841112</v>
+        <v>0.194311179159422</v>
       </c>
       <c r="FI2" t="n">
         <v>0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.04637578096568799</v>
+        <v>-0.1189974526004981</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.07084916398079287</v>
+        <v>0.04668994261656417</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
@@ -1512,25 +1512,25 @@
         <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.02735602551869211</v>
+        <v>0.3479978283540573</v>
       </c>
       <c r="FR2" t="n">
         <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.09799222437859922</v>
+        <v>-0.3759804956613098</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.07705834545184165</v>
+        <v>-0.4375973482718528</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
         <v>0</v>
@@ -1539,31 +1539,31 @@
         <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.03558398777213669</v>
+        <v>0.3348381349615659</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.03947378319382469</v>
+        <v>-0.2269400649505847</v>
       </c>
       <c r="GC2" t="n">
         <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -2137,22 +2137,22 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.03424270711996886</v>
+        <v>-0.1294999666114487</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1788847039688309</v>
+        <v>0.1033815553278723</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1077077391464403</v>
+        <v>-0.01944638343154684</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -2164,25 +2164,25 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01599956026901424</v>
+        <v>-0.1176025322754431</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05862026987620436</v>
+        <v>0.04112164288407898</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005881845223133167</v>
+        <v>-0.07842375126918985</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0</v>
@@ -2191,19 +2191,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.02028289155123418</v>
+        <v>0.02579668002257897</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1516176043021802</v>
+        <v>0.08755354701884334</v>
       </c>
       <c r="V4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.004522907116297402</v>
+        <v>-0.0963110015782125</v>
       </c>
       <c r="X4" t="n">
         <v>-0</v>
@@ -2212,52 +2212,52 @@
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.04004468374434664</v>
+        <v>0.08537677871078911</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.06484837682654</v>
+        <v>-0.1077467834635918</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06515944849276051</v>
+        <v>-0.1141110863646115</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03768861687125951</v>
+        <v>0.05954999749225057</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.05736204415839104</v>
+        <v>-0.109383592188832</v>
       </c>
       <c r="AN4" t="n">
         <v>-0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.09073587546919835</v>
+        <v>-0.07046702964722888</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2266,82 +2266,82 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.02631909787983101</v>
+        <v>-0.1046269865747054</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.3076472438123232</v>
+        <v>0.03558150360233991</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.5122886958248438</v>
+        <v>-0.3034950087648385</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0.1696341353561095</v>
+        <v>-0.07489520779261476</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.018021821964911</v>
+        <v>0.06340152564041469</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.01191853710037301</v>
+        <v>0.1873330783123599</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.07159653606620256</v>
+        <v>0.174028545031943</v>
       </c>
       <c r="BM4" t="n">
         <v>-0</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.1906465015556028</v>
+        <v>0.02458727105211552</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1602177306124544</v>
+        <v>-0.004276497288379141</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
@@ -2353,22 +2353,22 @@
         <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0.015717504938423</v>
+        <v>-0.1025433933379185</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.05812236687776219</v>
+        <v>0.1093765849138761</v>
       </c>
       <c r="BX4" t="n">
         <v>-0</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1160936469807805</v>
+        <v>-0.1139606004654532</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2380,22 +2380,22 @@
         <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.005808947708774969</v>
+        <v>0.08572907872608763</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF4" t="n">
-        <v>-0.05307883702826099</v>
+        <v>-0.01561485927686621</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.06584274410494073</v>
+        <v>0.05168216502858011</v>
       </c>
       <c r="CI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ4" t="n">
         <v>-0</v>
@@ -2407,22 +2407,22 @@
         <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0.0002996969493519485</v>
+        <v>-0.002286154988146584</v>
       </c>
       <c r="CN4" t="n">
         <v>0</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.03716113078529133</v>
+        <v>-0.009834165034183953</v>
       </c>
       <c r="CP4" t="n">
         <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1440520342294316</v>
+        <v>-0.02592690322140347</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
@@ -2434,22 +2434,22 @@
         <v>0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0.006213787287038312</v>
+        <v>0.07039206805764121</v>
       </c>
       <c r="CW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0.03175506583760332</v>
+        <v>-0.04004946463163786</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.01789368622912253</v>
+        <v>0.002193463814505553</v>
       </c>
       <c r="DA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB4" t="n">
         <v>0</v>
@@ -2461,100 +2461,100 @@
         <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.02386467633269128</v>
+        <v>0.01149234232256665</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001829635593989386</v>
+        <v>0.001415868439314069</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.1224589221103038</v>
+        <v>0.123468148872514</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0.1326685922629581</v>
+        <v>0.09903961902228726</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP4" t="n">
-        <v>-0.03911169251558103</v>
+        <v>0.1029837939638848</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.03260435501357514</v>
+        <v>-0.09309375060616891</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW4" t="n">
-        <v>-0.07047152912525283</v>
+        <v>-0.04277918234179993</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0.04357572313623153</v>
+        <v>0.2433067820217405</v>
       </c>
       <c r="DZ4" t="n">
         <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.05540498689003998</v>
+        <v>-0.18320836244037</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
         <v>-0</v>
       </c>
       <c r="EE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0.05881378361771702</v>
+        <v>0.07337002604305329</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0.091236360716826</v>
+        <v>0.01604382999896413</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.02329975128622987</v>
+        <v>0.01448193592765919</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
@@ -2563,55 +2563,55 @@
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>-0.07796452157512089</v>
+        <v>0.05173193513056144</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.02752564008650723</v>
+        <v>0.007975076929914154</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.1536650917833085</v>
+        <v>0.07292213245576104</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
         <v>-0</v>
       </c>
       <c r="EV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0.02595985766267161</v>
+        <v>0.0733922384716128</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ4" t="n">
-        <v>-0.03450461629234079</v>
+        <v>-0.05475201165475496</v>
       </c>
       <c r="FA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02506466535286903</v>
+        <v>0.02735088897276855</v>
       </c>
       <c r="FC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD4" t="n">
         <v>-0</v>
@@ -2623,46 +2623,46 @@
         <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.008070867032958182</v>
+        <v>0.2663674124415558</v>
       </c>
       <c r="FH4" t="n">
         <v>-0</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0.04954196388947833</v>
+        <v>0.04185557341377048</v>
       </c>
       <c r="FJ4" t="n">
         <v>0</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0428677171947657</v>
+        <v>-0.08336912752625286</v>
       </c>
       <c r="FL4" t="n">
         <v>-0</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.02129121423072506</v>
+        <v>0.1378635386521954</v>
       </c>
       <c r="FQ4" t="n">
         <v>-0</v>
       </c>
       <c r="FR4" t="n">
-        <v>-2.686227622133608e-05</v>
+        <v>0.002463730075264531</v>
       </c>
       <c r="FS4" t="n">
         <v>0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.005473736434400217</v>
+        <v>0.003619658894818117</v>
       </c>
       <c r="FU4" t="n">
         <v>0</v>
@@ -2671,34 +2671,34 @@
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0.06249883070916808</v>
+        <v>0.1528879584203245</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.01073643937819525</v>
+        <v>0.0006030886667644813</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
         <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6469892975275289</v>
+        <v>0.4078188652839695</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2613169655013686</v>
+        <v>-0.2220849108629945</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1491257851368513</v>
+        <v>-0.1021251319228285</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2733,22 +2733,22 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3691069686355855</v>
+        <v>0.3250992582821117</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2065312767424661</v>
+        <v>-0.2741812047421112</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1170638164617196</v>
+        <v>-0.09407557620557284</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5" t="n">
         <v>-0</v>
@@ -2760,28 +2760,28 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2391970916329945</v>
+        <v>0.09860087524625888</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.07782079283891351</v>
+        <v>-0.05920562857514831</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0011637993696573</v>
+        <v>-0.06507977112688233</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -2790,22 +2790,22 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2070709942200458</v>
+        <v>0.0393038434723521</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.01339474841885576</v>
+        <v>-0.09021202531046939</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.05028692009745169</v>
+        <v>0.007780572160676182</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2814,28 +2814,28 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.2091722976317852</v>
+        <v>0.2871969224181722</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.05837946086355724</v>
+        <v>-0.09499744938776093</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.1243200847951544</v>
+        <v>0.2135758630309817</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2844,43 +2844,43 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.9472007598173435</v>
+        <v>0.5880098034693573</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.1654427022981404</v>
+        <v>-0.2176383522769841</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.05197377577909063</v>
+        <v>-0.2309306680925213</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0995675281707309</v>
+        <v>-0.0960650268020477</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.03622981853003734</v>
+        <v>-0.06837194922885548</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.3523479990440295</v>
+        <v>-0.1545812194102988</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,28 +2895,28 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.06731213114210853</v>
+        <v>-0.1116965281309839</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.2135163169278082</v>
+        <v>0.006738843579187612</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.05360722189061928</v>
+        <v>0.01354194579812791</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
         <v>-0</v>
@@ -2925,19 +2925,19 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2907711952958063</v>
+        <v>0.285555828614671</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.06396347646294682</v>
+        <v>-0.1492648121132002</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.06095962305481919</v>
+        <v>-0.04070734766954896</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
@@ -2952,16 +2952,16 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1948368169172821</v>
+        <v>-0.2636855394092563</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.03116963056249061</v>
+        <v>0.1782390373532447</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.04006576359353791</v>
+        <v>-0.0009659113844667801</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2973,25 +2973,25 @@
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0245418317666287</v>
+        <v>-0.1491127523701299</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.06604732167949848</v>
+        <v>0.1119922855242155</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1433343095384792</v>
+        <v>0.06091810385087611</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
@@ -3003,49 +3003,49 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1744869331382168</v>
+        <v>-0.2590893954685947</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.08917009522333663</v>
+        <v>0.188311459784706</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.05430732993466653</v>
+        <v>0.02207622530918563</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.07528551895011919</v>
+        <v>-0.1213869015807779</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.001721170038604544</v>
+        <v>-0.00731014880737212</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.000239728245558333</v>
+        <v>0.002865774010070407</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>-0</v>
@@ -3060,16 +3060,16 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1335668367012667</v>
+        <v>-0.1350859666485285</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.007203204875725853</v>
+        <v>0.09332269977942935</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.06981862597095845</v>
+        <v>-0.06602171738746443</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -3087,22 +3087,22 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.05366714928948946</v>
+        <v>0.07413115184986796</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.05207771849065018</v>
+        <v>0.07660267240133971</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.08159355332257889</v>
+        <v>0.07198620708676899</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
         <v>0</v>
@@ -3114,49 +3114,49 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.04008851870708319</v>
+        <v>-0.2252226967304521</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.1566380619369285</v>
+        <v>0.1381718196800151</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.002770285063370737</v>
+        <v>0.06008704249115632</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.1515248309144965</v>
+        <v>-0.1633055998468612</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.02736506728932692</v>
+        <v>-0.105199492430266</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.05674055705419165</v>
+        <v>0.01739587002503496</v>
       </c>
       <c r="ET5" t="n">
         <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3168,46 +3168,46 @@
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1702306404910953</v>
+        <v>-0.2933538600562084</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.07268997977162771</v>
+        <v>0.2042493342901657</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.06189312601308809</v>
+        <v>0.006814643745802955</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.03970622083663944</v>
+        <v>-0.1461344655756522</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.1458322223006174</v>
+        <v>0.1086646989898067</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.002043911946107423</v>
+        <v>0.04570122605431291</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
@@ -3216,22 +3216,22 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
         <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.009966116483299699</v>
+        <v>0.01525470937024371</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.01705096626345516</v>
+        <v>0.2503980384188345</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.002026015918492723</v>
+        <v>-0.001078418470864957</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
@@ -3240,22 +3240,22 @@
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.0474358435416098</v>
+        <v>-0.2162596667352689</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.08949344690670749</v>
+        <v>0.1064925266080438</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
@@ -3267,10 +3267,10 @@
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.05466739640906878</v>
+        <v>0.4497720198174781</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,16 +3287,16 @@
         <v>-0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.04197564406358952</v>
+        <v>0.04998350377641669</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.02913400390991769</v>
+        <v>-0.2134015477221347</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3305,34 +3305,34 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02662921174603067</v>
+        <v>0.4391408047882604</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.03165495843168567</v>
+        <v>-0.08442150665807185</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01370883504416372</v>
+        <v>-0.09352583639760878</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002879667753235953</v>
+        <v>0.1429680644792816</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,52 +3341,52 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01026042306252359</v>
+        <v>-0.1487261980388352</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02185716431031935</v>
+        <v>-0.04604818139459244</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02184202434105669</v>
+        <v>0.02968971798121114</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01181450649233285</v>
+        <v>-0.2745709771371728</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.01035578080157751</v>
+        <v>-0.0668567648588007</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01688363862629536</v>
+        <v>0.1791051276941922</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01766166826188932</v>
+        <v>0.04730886225077274</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.00745536364271354</v>
+        <v>-0.1390206269175754</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,37 +3410,37 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.07240651733096537</v>
+        <v>0.6834224867284797</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.04520311074176789</v>
+        <v>-0.1934063433504269</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.02014869965103768</v>
+        <v>-0.2485532777009002</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.03130351973825705</v>
+        <v>0.03654981541839204</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,40 +3449,40 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.03042893935704419</v>
+        <v>-0.08078092096384161</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.02301297446176348</v>
+        <v>-0.1736988702272608</v>
       </c>
       <c r="BI6" t="n">
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0389081035073159</v>
+        <v>0.02576153880658297</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01772435713324906</v>
+        <v>0.09022205269006764</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.007809535938641675</v>
+        <v>0.05475446371582406</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.02008174618063341</v>
+        <v>0.283239731049771</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,37 +3503,37 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01593040397870063</v>
+        <v>-0.01860891281975947</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.003258582368397351</v>
+        <v>-0.1000798218844919</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.01145453787251219</v>
+        <v>-0.2286715305996118</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.01390470255950332</v>
+        <v>-0.04977160088256027</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.01412863011881516</v>
+        <v>0.1432564816085519</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
@@ -3542,109 +3542,109 @@
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.003460147362307554</v>
+        <v>-0.13829084190751</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
         <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.002372844868418098</v>
+        <v>0.06295781927560082</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.002373935022521611</v>
+        <v>0.09892487071815885</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.005683190302190417</v>
+        <v>-0.2177565534024656</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.01384914866586838</v>
+        <v>-0.0461412667727013</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.01887774154823333</v>
+        <v>0.1496357881693814</v>
       </c>
       <c r="DB6" t="n">
         <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.01484432935799966</v>
+        <v>-0.06543766688349854</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.007353847122105636</v>
+        <v>-0.1688303633761233</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.001016540396985719</v>
+        <v>0.06596744150125565</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.01072606377743174</v>
+        <v>-0.1018057751149967</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01804071116280199</v>
+        <v>-0.02870987931838521</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.01590050956677634</v>
+        <v>0.1287465682150401</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3656,25 +3656,25 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01298606008683245</v>
+        <v>0.01010699124575043</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01207085996899307</v>
+        <v>0.02972807495255808</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.00872351472938988</v>
+        <v>0.09303352210129197</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
@@ -3683,34 +3683,34 @@
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.009299584430593744</v>
+        <v>-0.07256229292441138</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0032992700217724</v>
+        <v>-0.1169934384064782</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.01381455853213522</v>
+        <v>0.04169687138485767</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.01249903305946648</v>
+        <v>-0.1284005615975841</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
@@ -3719,79 +3719,79 @@
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0183613029495876</v>
+        <v>-0.1327481171538397</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.01513623147616226</v>
+        <v>0.1933761879681172</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.001842013015646086</v>
+        <v>-0.2321150058538939</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0115004210802759</v>
+        <v>-0.08591958255237295</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01820991349123877</v>
+        <v>0.130018983666867</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.02233208816382262</v>
+        <v>-0.2708899071034195</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02688384865528886</v>
+        <v>0.0226241194042815</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01319244325687779</v>
+        <v>0.2928644575972612</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.001217214064337474</v>
+        <v>0.02456788049553749</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
@@ -3800,25 +3800,25 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.000260091430757718</v>
+        <v>0.006240158959041048</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.01924970764424324</v>
+        <v>0.08836695288477188</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02417490658904577</v>
+        <v>-0.03222138412406363</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
@@ -3827,13 +3827,13 @@
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.002723083369022944</v>
+        <v>0.05916883089022524</v>
       </c>
       <c r="GE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF6" t="n">
         <v>0</v>
@@ -4413,160 +4413,160 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.9326095860668535</v>
+        <v>0.3269267894183425</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.47994012660163</v>
+        <v>-0.0822050343281734</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3245907341539616</v>
+        <v>-0.07399937263018898</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5632618300840739</v>
+        <v>0.2809660198943653</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2989042195931942</v>
+        <v>-0.1749035262228468</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3407295474354117</v>
+        <v>-0.1515116667703137</v>
       </c>
       <c r="O8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2004484167565346</v>
+        <v>0.09043537503996986</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2680215321204487</v>
+        <v>-0.08293397890019666</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2845892749633017</v>
+        <v>-0.05351054038145208</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
         <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.2062739773072498</v>
+        <v>-0.04198356940543891</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.07291688235280751</v>
+        <v>-0.08721699169108332</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.0121274349262715</v>
+        <v>-0.1327202207969861</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.2510693725879663</v>
+        <v>0.1680755188635832</v>
       </c>
       <c r="AM8" t="n">
         <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.007028865218214825</v>
+        <v>-0.04843623615804438</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.2364984885291462</v>
+        <v>0.08758021524281043</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>-1.065211751120239</v>
+        <v>0.3561035330256662</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2675561239711146</v>
+        <v>-0.03357741172896474</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1805795429629934</v>
+        <v>-0.2148805704600242</v>
       </c>
       <c r="AY8" t="n">
         <v>-0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4575,127 +4575,127 @@
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.1375445590271753</v>
+        <v>-0.009066631732301166</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.02614234362155999</v>
+        <v>-0.06350348874172686</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.366114035688948</v>
+        <v>-0.1659047249405125</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>-0.1936130025504135</v>
+        <v>-0.01408359598839778</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>-0.2295312086737682</v>
+        <v>-0.03177639137289585</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.1814158653850303</v>
+        <v>0.03596857764022812</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>-0.3736020874485588</v>
+        <v>0.1939039915805724</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.1576748079664946</v>
+        <v>-0.09491181218228863</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.2697874030320582</v>
+        <v>-0.04178233091723005</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.2102920391231728</v>
+        <v>-0.1379479367556219</v>
       </c>
       <c r="CF8" t="n">
         <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>-0.03834219949203629</v>
+        <v>0.06255012474311418</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.02009565958380019</v>
+        <v>0.0184156268315165</v>
       </c>
       <c r="CI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL8" t="n">
         <v>-0</v>
       </c>
       <c r="CM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.05105800423403315</v>
+        <v>-0.0831540747641191</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.1336840800312032</v>
+        <v>0.1237750559708629</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.06125566424275346</v>
+        <v>0.08838810256498558</v>
       </c>
       <c r="CR8" t="n">
         <v>-0</v>
@@ -4704,52 +4704,52 @@
         <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.1911048409217154</v>
+        <v>-0.125049032689553</v>
       </c>
       <c r="CX8" t="n">
         <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0.1257697770000861</v>
+        <v>0.06676761004578818</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.009988547985123476</v>
+        <v>0.03269436764288632</v>
       </c>
       <c r="DA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
         <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.001220420975125926</v>
+        <v>-0.05959045110625194</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.01871974921068379</v>
+        <v>-0.004020593065012057</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001765733577125547</v>
+        <v>-0.02354803763039624</v>
       </c>
       <c r="DJ8" t="n">
         <v>-0</v>
@@ -4758,52 +4758,52 @@
         <v>-0</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.2396862395238072</v>
+        <v>-0.08690674230586055</v>
       </c>
       <c r="DP8" t="n">
         <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.009028330901492099</v>
+        <v>0.02238644996484316</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.04336824835496132</v>
+        <v>0.03685174087513828</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>-0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.07315645092427273</v>
+        <v>0.009441952911867739</v>
       </c>
       <c r="DY8" t="n">
         <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.03776854633582032</v>
+        <v>0.02920600946883837</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.136878740297997</v>
+        <v>0.08919809229239446</v>
       </c>
       <c r="EB8" t="n">
         <v>0</v>
@@ -4812,88 +4812,88 @@
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.01566109958660093</v>
+        <v>-0.07355514913227935</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>-0.1536131953041196</v>
+        <v>0.02349403412972951</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.1076050249365564</v>
+        <v>0.007098262861039832</v>
       </c>
       <c r="EK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
         <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.09261908444334914</v>
+        <v>-0.05012872928492992</v>
       </c>
       <c r="EQ8" t="n">
         <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>-0.01598613654895617</v>
+        <v>-0.02120563510535419</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.1154750739161463</v>
+        <v>-0.05751059108599262</v>
       </c>
       <c r="ET8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.1433013923222067</v>
+        <v>-0.1486743796964302</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>-0.09768328386047073</v>
+        <v>0.07491843816865569</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.03028390404556062</v>
+        <v>0.007258480530890302</v>
       </c>
       <c r="FC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
         <v>-0</v>
@@ -4902,22 +4902,22 @@
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.06937950711264823</v>
+        <v>-0.1558149025729975</v>
       </c>
       <c r="FI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>-0.2333023508892805</v>
+        <v>0.1073716367564408</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.04433489931717523</v>
+        <v>0.1223143559916913</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
         <v>0</v>
@@ -4929,49 +4929,49 @@
         <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.05622669814680393</v>
+        <v>0.03928520511453287</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.01335038980521064</v>
+        <v>0.2100321637551846</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.2281483848119918</v>
+        <v>-0.00204353786658899</v>
       </c>
       <c r="FU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
         <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01397405375793199</v>
+        <v>-0.08820257023064378</v>
       </c>
       <c r="GA8" t="n">
         <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.03196371879114728</v>
+        <v>-0.008466441297049758</v>
       </c>
       <c r="GC8" t="n">
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
         <v>-0</v>
@@ -4985,19 +4985,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4833198792730434</v>
+        <v>-0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7135491436484558</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0660634871058655</v>
+        <v>-0</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -5012,79 +5012,79 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4277062705514525</v>
+        <v>-0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6104266452165374</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1208425148922357</v>
+        <v>-0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1705621217680103</v>
+        <v>-0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06599901531561342</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.02629756446926284</v>
+        <v>-0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.1353929655075868</v>
+        <v>-0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.08224659415777193</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.008813588348748184</v>
+        <v>-0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -5093,49 +5093,49 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.1257750575820272</v>
+        <v>-0</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.04239132975653433</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.110382303920312</v>
+        <v>-0</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.4255363206787944</v>
+        <v>-0</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2953009514067182</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.02315703070788774</v>
+        <v>-0</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
         <v>0</v>
@@ -5147,16 +5147,16 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.1756158337460701</v>
+        <v>-0</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.2290542428493975</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.1603157186123782</v>
+        <v>-0</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.0397162402412827</v>
+        <v>-0</v>
       </c>
       <c r="BN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.02376266005538523</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.1910672462887686</v>
+        <v>-0</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
@@ -5201,43 +5201,43 @@
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.179825793953457</v>
+        <v>-0</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.1173546898722072</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.07023752371601336</v>
+        <v>-0</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.08768469584134049</v>
+        <v>-0</v>
       </c>
       <c r="CF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.1372905954041265</v>
+        <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.02459571922287377</v>
+        <v>-0</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
@@ -5246,28 +5246,28 @@
         <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.01447221512890787</v>
+        <v>-0</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.03226921509020528</v>
+        <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.07355493804416789</v>
+        <v>-0</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS9" t="n">
         <v>0</v>
@@ -5276,79 +5276,79 @@
         <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.1022564438136476</v>
+        <v>0</v>
       </c>
       <c r="CX9" t="n">
         <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0.1308327872954535</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.008184521352514764</v>
+        <v>0</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.309396649929827</v>
+        <v>-0</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0.1054621350059188</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.01552988020853691</v>
+        <v>-0</v>
       </c>
       <c r="DJ9" t="n">
         <v>0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.003072610678194399</v>
+        <v>-0</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.007354445571896141</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.05514788779030101</v>
+        <v>-0</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT9" t="n">
         <v>0</v>
@@ -5357,49 +5357,49 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.08790654122059251</v>
+        <v>0</v>
       </c>
       <c r="DY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.1186515381518493</v>
+        <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.05593786692625178</v>
+        <v>0</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.06626303381215927</v>
+        <v>-0</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.150736217061881</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.05463299310092886</v>
+        <v>-0</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
@@ -5417,16 +5417,16 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1080122397101147</v>
+        <v>-0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.05716178894233055</v>
+        <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01482405473264862</v>
+        <v>-0</v>
       </c>
       <c r="ET9" t="n">
         <v>0</v>
@@ -5435,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
         <v>0</v>
@@ -5444,43 +5444,43 @@
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.1040170752977869</v>
+        <v>-0</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.1319020110310607</v>
+        <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0268268875263237</v>
+        <v>-0</v>
       </c>
       <c r="FC9" t="n">
         <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.04173785303107523</v>
+        <v>-0</v>
       </c>
       <c r="FI9" t="n">
         <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>-0.03886740128262213</v>
+        <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.001758381342018882</v>
+        <v>-0</v>
       </c>
       <c r="FL9" t="n">
         <v>0</v>
@@ -5489,52 +5489,52 @@
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.06831995746826294</v>
+        <v>0</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.06278606320707832</v>
+        <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.02138486330652123</v>
+        <v>0</v>
       </c>
       <c r="FU9" t="n">
         <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY9" t="n">
         <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.04194517743131326</v>
+        <v>0</v>
       </c>
       <c r="GA9" t="n">
         <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.04405072478428362</v>
+        <v>0</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.652096176726214</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,25 +5563,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0</v>
+        <v>-0.06156335971873612</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.3255430755519068</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.6714031020357276</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,52 +5590,52 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0</v>
+        <v>-0.257728968776153</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.1163690841322542</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.2564978263224711</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0</v>
+        <v>-0.09526279336759334</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.005739717336078093</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>-0.1201801052700496</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -5644,43 +5644,43 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0</v>
+        <v>-0.3839251907840454</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>0.07634821363817798</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>0.2795695942664531</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0</v>
+        <v>0.09061547942920581</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>-0.1110189261873751</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>0.9550256186439994</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5698,25 +5698,25 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0</v>
+        <v>-0.2081920533232033</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>-0.3336083323103009</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>-0.1384240835536156</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,16 +5725,16 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0</v>
+        <v>-0.2941979558342336</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0.08500411076067858</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,19 +5743,19 @@
         <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>0.05136581946550946</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0</v>
+        <v>0.09194586268674133</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>0.1851004374706798</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
@@ -5767,49 +5767,49 @@
         <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>0.5060566491609747</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0</v>
+        <v>-0.01047176027958364</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>-0.1039173478618142</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0</v>
+        <v>-0.2648276107019183</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0</v>
+        <v>-0.000955706503686329</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>0.1831376386395401</v>
       </c>
       <c r="CJ10" t="n">
         <v>0</v>
@@ -5818,40 +5818,40 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0</v>
+        <v>-0.2882962014811543</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0</v>
+        <v>0.312569906714709</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0.03891294311650242</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0</v>
+        <v>-0.2414947934834948</v>
       </c>
       <c r="CX10" t="n">
         <v>0</v>
@@ -5860,16 +5860,16 @@
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0</v>
+        <v>0.04275947051254629</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>0.197661352065611</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
@@ -5878,19 +5878,19 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0</v>
+        <v>-0.2969934264053421</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0</v>
+        <v>-0.1841800151350677</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>0.169583126647911</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
@@ -5899,94 +5899,94 @@
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0</v>
+        <v>-0.1649876524381626</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0</v>
+        <v>0.1023096710371678</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>0.02115082999542795</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0</v>
+        <v>-0.01418844139815797</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0</v>
+        <v>-0.04135648893259199</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>0.09653592119387842</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0</v>
+        <v>-0.1265493937700215</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0</v>
+        <v>-0.04461931931274541</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>0.02320395719883718</v>
       </c>
       <c r="EL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0</v>
+        <v>-0.2117102574974506</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,13 +5995,13 @@
         <v>0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0</v>
+        <v>-0.2669726016363238</v>
       </c>
       <c r="ET10" t="n">
-        <v>0</v>
+        <v>-0.3015473967709593</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6010,22 +6010,22 @@
         <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0</v>
+        <v>-0.3016731859651918</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0</v>
+        <v>0.02153374677444921</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>0.1893263034542909</v>
       </c>
       <c r="FD10" t="n">
         <v>0</v>
@@ -6034,25 +6034,25 @@
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0</v>
+        <v>-0.2426642896675731</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0</v>
+        <v>0.1665786604709661</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>0.1743805008821849</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
@@ -6067,55 +6067,3469 @@
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0</v>
+        <v>0.04621423386911228</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0</v>
+        <v>0.01831842658815099</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>0.0815051797298966</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
         <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
         <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0</v>
+        <v>-0.1373304175996975</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0</v>
+        <v>0.0999684673332025</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.4245266890350684</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1576987805325897</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1352052090425414</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.4252528348257628</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2643651157897504</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2138756348093349</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.05017049743406231</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.09914932995301881</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.001824937501993645</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.07306406208989251</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.05413619540634573</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.005864142291293964</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.282105980055827</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.06858468959043686</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.2446055919049445</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.2585242710119277</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.1335215802967511</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.1864331135031091</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.03418551766888916</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.03904040242141571</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.2182855476170716</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.1575393068532555</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.07512054374017547</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.06703937608637835</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.350923335358912</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.1428118954674168</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.0194899928896454</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.2849248231785644</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>-0.07316676595040243</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.02082724980616584</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.1656120125444826</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-0.1832765740189027</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.1066289229453656</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.2795652145563891</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0.06688983416284022</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.00396380779779463</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.1911826725071984</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>-0.03425608590263768</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.09143884909027357</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.1283871674495966</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0.08137928205320154</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.0410240450741025</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0.1010276291135733</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0.105471219627893</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>-0.2154387209004109</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.2193482586486327</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>-0.00865336821254057</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0.03327925386550532</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.1756519901397739</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0.04098117427100181</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.05832453642563235</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.3099847232511844</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>-0.09383222974901159</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.008536134711430558</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1763726162964709</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>-0.07960511060294657</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.1205969785367497</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>-0.1344733084399541</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>-0.2359312091105541</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.01855694219724938</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.1871206073609845</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>-0.03058528121324822</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3684267170628243</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.05260725468658067</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2040563022200743</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4158162633332303</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.06242929646453908</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.2139265395936029</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.08938481934816656</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.008981190279130039</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.02226434318801148</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.01281481013157385</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.134983741457754</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.01142246644957475</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.07253074864154106</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.03256430008355941</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.04528951828106919</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.363825742795196</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.1525896930029862</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.1086174891205462</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.04400863627353224</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.02901475070553247</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.07150262752023233</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.02888317647488737</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.08314599799564937</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.05044347129673669</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.2043313734826456</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.003958887016750674</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.08857739448037769</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.1238132828281052</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.00540339096146104</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.08410303766239983</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.007697392664297743</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.04969647151950234</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.01976876347639689</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.1169080145450514</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.002459514204280111</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.1024929047564807</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>-0.03445442290351065</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-0.06166004741639292</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.04712040292566542</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.001860063619889603</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.0641163391882959</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>-0.07339289402936998</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.08541033507565671</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.03444233192972031</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.02931097244602215</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.0475668486250039</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.04615538985462623</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.04377665450060202</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.03725110466782544</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>-0.01200055082856464</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.007378408704410038</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.1280420849284551</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.02860971187202945</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.07495329996703184</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.1320934021706255</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.01096837879775794</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.1269419876601402</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.176732055857469</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.03342740509854874</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.05459934185347431</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.03111418274587318</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.06164018499401686</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.8450606578248143</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4393772276329831</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1805941336011623</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7621552005516459</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.7027961505584737</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.08668293937080815</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.1315829246129884</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.1122584561253427</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.01311466242505138</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.1276660793981693</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.2602882082969309</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.1042431784757727</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.2224531338133103</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.1131157589403994</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.2376842315012229</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.5696514636145831</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.2757063022034184</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.2179760874422034</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.01390483243493431</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.09104277803000431</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.08274068303773442</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-0.06371001971903638</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0.009237300776718792</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.07327385005955203</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.322380482392493</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-0.2915228345630919</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.06190980346780603</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.2830712095343573</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.1882605328275508</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.06983507267911285</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.02027119671884909</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.2509334247353226</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.1945376525806031</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.2677898749528451</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.2050728405314169</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-9.257415561439023e-05</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.06084332467350063</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.1008625663663499</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.01935755808842167</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.1986175943938703</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.05803090764803018</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.04495813330061545</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.05484951213094413</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>-0.04256863603086698</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.1752108319952129</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>-0.2486123979103778</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.1711406397211934</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.03432354847707823</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.1670105444442713</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.1637856152366127</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.1442434200671101</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.3304602603518282</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.2294783905827135</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.07000142222746158</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>-0.08455041998623229</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>-0.2113616897850983</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>-0.1576942937511839</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>-0.4069023875878521</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>-0.04704851272755624</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.1261268741742353</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.1351073532633857</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.04422671774878432</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>-0.2401423523755042</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1542935968862869</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2686533885018212</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.211429159948543</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.253140721965848</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.4372034054635657</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.006397943999695186</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.001926033754725506</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0649898351439787</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.002871407131363233</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.02704438949665484</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.042543926305602</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.05353066032888073</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.1068370681452114</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.04229117884336654</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.2415387651322365</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.09294897001451953</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.4077745881543662</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.01140971093190836</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.1432370835034973</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.08498266796526649</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.07026024271831638</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.04820259607561714</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.01909341244510063</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.08964150963745983</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.09869201796128453</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.2185156289192213</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.07913600949182849</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>-0.04404220801852851</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>-0.08501883787881118</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.002437995628981819</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-0.08869281180209539</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>-0.08954153172457725</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.09515527850631457</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>-0.08449498790593922</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>-0.09681672102158921</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.003623638009578875</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.02941247957170811</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>-0.03417451999661677</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.01649867559328214</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.03914021113781726</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>-0.1123995232896319</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.03902798113747152</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>-0.1407167613675103</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>-0.09251000968941239</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.01450877527947947</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>-0.05151023199289034</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.03066815740558202</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>-0.04038032106621476</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.01216206159287782</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>-0.05407775410948825</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0.09016405325185708</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>-0.06104148893166261</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>-0.09276395170202867</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0.1108066339782013</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.04637119433854722</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>-0.03367339099894784</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.1358834249202498</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.01309442271653696</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.1993874224724395</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>-0.009328445884885777</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.03602058179106425</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.4187329736450701</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0567004901587551</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.2292775941081757</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5377136285692491</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.04966225331920024</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.2600475217735947</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.08695253121364752</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.06120834722452442</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.005188920654061755</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.02300788629125439</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.2561626787333297</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.05652526695222376</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.04652348941513801</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.0104683836210958</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.039384024127494</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.4557574771450126</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.1965029497352193</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.1041939070203756</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.0156747791671278</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.02158748001924546</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-0.07904580930996728</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.03536651615907869</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.04632438868064834</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.03847761847369213</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.283433773055254</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.03156957084731336</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-0.07741615968468983</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.1205803989145212</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.003412483072892288</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.08795562994327179</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.1517609358999238</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.1125066143712398</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.09506579145399989</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.1217957449910852</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>-0.01759227515277677</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.09787022262186834</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.03238769623536238</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0.1750372717984032</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>-0.001021686494344835</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0.02503559492998633</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0.04266209772094262</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>-0.01155291726952748</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0.03043550919859175</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0.07672696483689923</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0.02771009832678378</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.03589614065460017</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0.03907345239645291</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.03491826135882444</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0.05479087941665152</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.01782810258532639</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.02310828003822</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.1270328604433202</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0.02902988922135494</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.06390479902192413</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.160615103609863</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.02710278157203818</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.1500358118763957</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>-0.2003925422269331</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.09660772113508605</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>-0.005961838439198829</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.06980285243338796</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.05916385242995312</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1769315697456137</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.06908676952894123</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.01602781355960925</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.1890165214582398</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.09198440762906435</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.03476171262309764</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.04414664906229598</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.02009586715998911</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.01598147138821759</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.0378209284771543</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.0471958732579781</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.03056487468726375</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.04443000396096987</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0.03306719885516635</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.03928328236181131</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.1495525742570972</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0.03351108487434444</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.06613095840542273</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.01877018465981296</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0.03734826217458041</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0.006315180938507081</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0.01857554853713392</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.01185068263785275</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.01992136218522069</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.1202049404267585</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>-0.04417206021293277</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0.009253031757141131</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0.04694764857750483</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.04254790132185243</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.0009340483321145136</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0.04993452387565841</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0.04728440008771312</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0.006094402029142412</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-0.0463711238962469</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0.04647185692216019</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.002809518288694227</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0.05465480803249217</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0.0286957842699363</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0.0244172652138239</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0.01145665545924969</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0.003914568316148295</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0.003647357907544075</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>-0.016211124481404</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0.04707684790181691</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0.00835810534083916</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0.04350379939967364</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0.03964934021293312</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0.01806896192911429</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0.02342096467266661</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0.03238337967983645</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0.003215957023343837</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0.05272275377842347</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0.05546689683682088</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0.00472969339575249</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0.04115225340139303</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0.02431493062984192</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0.01568126050263997</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>-0.05448555539736285</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0.02701564238401281</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0.09893634543508774</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>-0.04750220508622006</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0.02589097465892749</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
